--- a/data/trans_dic/P32E$calle_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P32E$calle_2023-Estudios-trans_dic.xlsx
@@ -490,7 +490,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en la calle</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en la calle (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,25; 47,42</t>
+          <t>12,8; 48,61</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 48,12</t>
+          <t>0,0; 60,66</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>12,38; 42,35</t>
+          <t>11,81; 43,97</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>11,18; 31,74</t>
+          <t>10,29; 29,72</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,49; 25,48</t>
+          <t>2,64; 27,62</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,66; 27,12</t>
+          <t>10,2; 25,59</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,82</t>
+          <t>0,0; 26,34</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,56; 51,7</t>
+          <t>9,23; 49,75</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,97; 33,23</t>
+          <t>7,81; 36,6</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,54; 27,48</t>
+          <t>12,44; 28,32</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,47; 32,41</t>
+          <t>8,47; 33,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>13,14; 25,5</t>
+          <t>12,68; 25,07</t>
         </is>
       </c>
     </row>
@@ -774,7 +774,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que, al menos, realiza el atracón de alcohol en la calle</t>
+          <t>Población que, al menos, realiza el atracón de alcohol en la calle (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3319; 12846</t>
+          <t>3468; 13168</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 2395</t>
+          <t>0; 3019</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3970; 13578</t>
+          <t>3787; 14099</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>10238; 29075</t>
+          <t>9421; 27225</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>571; 5848</t>
+          <t>606; 6339</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>12212; 31066</t>
+          <t>11677; 29313</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 7282</t>
+          <t>0; 6655</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2501; 13523</t>
+          <t>2413; 13012</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4098; 17090</t>
+          <t>4016; 18823</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>18051; 39551</t>
+          <t>17908; 40762</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4578; 17527</t>
+          <t>4580; 18054</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>26016; 50504</t>
+          <t>25103; 49650</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P32E$calle_2023-Estudios-trans_dic.xlsx
+++ b/data/trans_dic/P32E$calle_2023-Estudios-trans_dic.xlsx
@@ -549,17 +549,17 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>28,02%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>25,36%</t>
+          <t>23,53%</t>
         </is>
       </c>
     </row>
@@ -572,17 +572,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>12,8; 48,61</t>
+          <t>11,51; 45,35</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 60,66</t>
+          <t>0,0; 51,49</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>11,81; 43,97</t>
+          <t>11,64; 41,12</t>
         </is>
       </c>
     </row>
@@ -599,17 +599,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>10,04%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>17,16%</t>
+          <t>15,22%</t>
         </is>
       </c>
     </row>
@@ -622,17 +622,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>10,29; 29,72</t>
+          <t>10,1; 29,1</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>2,64; 27,62</t>
+          <t>2,07; 20,02</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,2; 25,59</t>
+          <t>8,94; 23,83</t>
         </is>
       </c>
     </row>
@@ -649,17 +649,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>8,81%</t>
+          <t>9,01%</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>26,75%</t>
+          <t>25,82%</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,52%</t>
         </is>
       </c>
     </row>
@@ -672,17 +672,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,34</t>
+          <t>0,0; 29,64</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>9,23; 49,75</t>
+          <t>10,22; 50,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,81; 36,6</t>
+          <t>7,79; 35,24</t>
         </is>
       </c>
     </row>
@@ -699,17 +699,17 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>17,54%</t>
         </is>
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>18,2%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18,69%</t>
+          <t>17,08%</t>
         </is>
       </c>
     </row>
@@ -722,17 +722,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>12,44; 28,32</t>
+          <t>11,47; 25,95</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>8,47; 33,38</t>
+          <t>7,8; 28,64</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,68; 25,07</t>
+          <t>12,08; 23,86</t>
         </is>
       </c>
     </row>
@@ -856,17 +856,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>7591</t>
+          <t>7623</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>612</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>8133</t>
+          <t>8235</t>
         </is>
       </c>
     </row>
@@ -879,17 +879,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>3468; 13168</t>
+          <t>3358; 13226</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>0; 3019</t>
+          <t>0; 3001</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>3787; 14099</t>
+          <t>4073; 14388</t>
         </is>
       </c>
     </row>
@@ -929,17 +929,17 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
-          <t>17356</t>
+          <t>18125</t>
         </is>
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>2303</t>
+          <t>2357</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>19659</t>
+          <t>20481</t>
         </is>
       </c>
     </row>
@@ -952,17 +952,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>9421; 27225</t>
+          <t>10558; 30417</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>606; 6339</t>
+          <t>623; 6018</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>11677; 29313</t>
+          <t>12040; 32070</t>
         </is>
       </c>
     </row>
@@ -1002,17 +1002,17 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>2225</t>
+          <t>2426</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>6996</t>
+          <t>7121</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>9221</t>
+          <t>9547</t>
         </is>
       </c>
     </row>
@@ -1025,17 +1025,17 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 6655</t>
+          <t>0; 7979</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>2413; 13012</t>
+          <t>2819; 14047</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>4016; 18823</t>
+          <t>4247; 19202</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>27172</t>
+          <t>28174</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>9842</t>
+          <t>10090</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>37014</t>
+          <t>38264</t>
         </is>
       </c>
     </row>
@@ -1098,17 +1098,17 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>17908; 40762</t>
+          <t>18420; 41677</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>4580; 18054</t>
+          <t>4950; 18175</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>25103; 49650</t>
+          <t>27078; 53476</t>
         </is>
       </c>
     </row>
